--- a/assets/files/visa-financial-model.xlsx
+++ b/assets/files/visa-financial-model.xlsx
@@ -7,13 +7,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income Statement" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key Ratios" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peer Comps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income Statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key Ratios" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peer Comps" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Valuation Summary'!$A$1:$E$27</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -25,7 +28,7 @@
     <numFmt numFmtId="165" formatCode="0.0&quot;x&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -167,8 +170,13 @@
       <color rgb="00595959"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -207,6 +215,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEF2F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E5496"/>
       </patternFill>
     </fill>
   </fills>
@@ -319,7 +337,7 @@
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -547,6 +565,13 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -796,6 +821,322 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" style="35" min="1" max="1"/>
+    <col width="24" customWidth="1" style="35" min="2" max="2"/>
+    <col width="14" customWidth="1" style="35" min="3" max="3"/>
+    <col width="14" customWidth="1" style="35" min="4" max="4"/>
+    <col width="14" customWidth="1" style="35" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="85" t="inlineStr">
+        <is>
+          <t>Visa Inc. (V) — Multi-Method Valuation Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="34" t="inlineStr">
+        <is>
+          <t>USD; per-share USD. Payments network — forward-P/E anchored (vs Mastercard). Live $356 (Jul 2026), 1,880M shares, net debt ~$5bn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="86" t="inlineStr">
+        <is>
+          <t>KEY INPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>Live share price ($)</t>
+        </is>
+      </c>
+      <c r="B5" s="87" t="n">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>Shares (M)</t>
+        </is>
+      </c>
+      <c r="B6" s="87" t="n">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>Net debt ($M)</t>
+        </is>
+      </c>
+      <c r="B7" s="87" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>FY25 adj EPS ($)</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="n">
+        <v>11.47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>FY26E adj EPS ($)</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="n">
+        <v>13.09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="34" t="inlineStr">
+        <is>
+          <t>FY26E EBITDA ($M)</t>
+        </is>
+      </c>
+      <c r="B10" s="87" t="n">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="34" t="inlineStr">
+        <is>
+          <t>Normalized FCF ($M)</t>
+        </is>
+      </c>
+      <c r="B11" s="87" t="n">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>Dividend/share ($)</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="n">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="86" t="inlineStr">
+        <is>
+          <t>VALUATION METHODS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="88" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B15" s="88" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="C15" s="88" t="inlineStr">
+        <is>
+          <t>Value/share ($)</t>
+        </is>
+      </c>
+      <c r="D15" s="88" t="inlineStr">
+        <is>
+          <t>vs price</t>
+        </is>
+      </c>
+      <c r="E15" s="88" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>P/E (relative, vs Mastercard)</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="inlineStr">
+        <is>
+          <t>29x × FY26E adj EPS</t>
+        </is>
+      </c>
+      <c r="C16" s="89">
+        <f>29*B9</f>
+        <v/>
+      </c>
+      <c r="D16" s="90">
+        <f>C16/B5-1</f>
+        <v/>
+      </c>
+      <c r="E16" s="91" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>EV/EBITDA (relative)</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>23x × FY26E EBITDA</t>
+        </is>
+      </c>
+      <c r="C17" s="89">
+        <f>(23*B10-B7)/B6</f>
+        <v/>
+      </c>
+      <c r="D17" s="90">
+        <f>C17/B5-1</f>
+        <v/>
+      </c>
+      <c r="E17" s="91" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>DCF (conservative floor)</t>
+        </is>
+      </c>
+      <c r="B18" s="34" t="inlineStr">
+        <is>
+          <t>FCF, WACC 8%, term g 4%</t>
+        </is>
+      </c>
+      <c r="C18" s="89" t="n">
+        <v>315</v>
+      </c>
+      <c r="D18" s="90">
+        <f>C18/B5-1</f>
+        <v/>
+      </c>
+      <c r="E18" s="91" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="34" t="inlineStr">
+        <is>
+          <t>(Reference) current market multiple</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="inlineStr">
+        <is>
+          <t>~27x FY26E EPS</t>
+        </is>
+      </c>
+      <c r="C19" s="89">
+        <f>B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="86" t="inlineStr">
+        <is>
+          <t>BLENDED VALUATION &amp; RATING</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="34" t="inlineStr">
+        <is>
+          <t>Blended fair value ($)</t>
+        </is>
+      </c>
+      <c r="B22" s="89">
+        <f>SUMPRODUCT(C16:C18,E16:E18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="34" t="inlineStr">
+        <is>
+          <t>Price upside/(downside) vs $356</t>
+        </is>
+      </c>
+      <c r="B23" s="90">
+        <f>B22/B5-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="34" t="inlineStr">
+        <is>
+          <t>Dividend yield</t>
+        </is>
+      </c>
+      <c r="B24" s="90">
+        <f>B12/B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="34" t="inlineStr">
+        <is>
+          <t>Total expected return</t>
+        </is>
+      </c>
+      <c r="B25" s="90">
+        <f>B23+B24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="34" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="B26" s="34">
+        <f>IF(B23&gt;0.10,"BUY",IF(B23&gt;0.03,"ACCUMULATE",IF(B23&gt;-0.08,"HOLD","REDUCE")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="34" t="inlineStr">
+        <is>
+          <t>Note: a payments network is best valued on forward earnings vs Mastercard; EV/EBITDA cross-checks and a DCF floor sit lower, as they under-price the toll-booth moat. After the run to ~$356, price upside has compressed.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A14:E14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="FF1A1F71"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1456,7 +1797,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="FF1A1F71"/>
@@ -2371,7 +2712,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="FF1A1F71"/>
@@ -3098,7 +3439,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="FF1A1F71"/>
@@ -3811,7 +4152,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001A1F71"/>
